--- a/public/downloads/에베레스트_원가분석서.xlsx
+++ b/public/downloads/에베레스트_원가분석서.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5361" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5361" uniqueCount="595">
   <si>
     <t>📘 EVEREST RESTAURANT GROUP · 메뉴 원가 분석서</t>
   </si>
@@ -110,10 +110,10 @@
     <t>▸  계산 방식</t>
   </si>
   <si>
-    <t>g당 단가</t>
-  </si>
-  <si>
-    <t>구매가격 ÷ 총중량(g)</t>
+    <t>단가</t>
+  </si>
+  <si>
+    <t>무게 품목: 구매가격 ÷ 총중량(g) → 원/g   ·   개수 품목: 구매가격 ÷ 규격수량 → 원/개</t>
   </si>
   <si>
     <t>재료비</t>
@@ -1431,10 +1431,10 @@
     <t>디저트 (굴랍자문 또는 라스굴라)</t>
   </si>
   <si>
-    <t>노란 셀(구매가격·규격)만 수정하세요. g당 단가와 전체 메뉴 원가가 자동으로 다시 계산됩니다.</t>
-  </si>
-  <si>
-    <t>💡  g당 단가 = 구매가격 ÷ 총중량(g).  총중량이 0이면 0원으로 처리되어 오류가 나지 않습니다(개당 판매 품목 등).</t>
+    <t>노란 셀(구매가격·규격)만 수정하세요. 단가와 전체 메뉴 원가가 자동으로 다시 계산됩니다.</t>
+  </si>
+  <si>
+    <t>💡  무게로 사는 것은 단가 = 구매가격 ÷ 총중량(g).  캔·포장용기처럼 개수로 사는 것은 단가 = 구매가격 ÷ 규격수량(원/개).</t>
   </si>
   <si>
     <t>식재료명</t>
@@ -1449,6 +1449,9 @@
     <t>총중량(g)</t>
   </si>
   <si>
+    <t>단가 (원/g·원/개)</t>
+  </si>
+  <si>
     <t>kg</t>
   </si>
   <si>
@@ -1491,7 +1494,7 @@
     <t>콜라_24개</t>
   </si>
   <si>
-    <t>⚠ 중량(g) 입력 필요 · 개당 품목</t>
+    <t>⚠ 총중량(g) 입력 필요 — 개수 품목이면 「개수 단위」로 바꾸세요</t>
   </si>
   <si>
     <t>사이다_24개</t>
@@ -31265,7 +31268,7 @@
         <v>474</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>201</v>
+        <v>475</v>
       </c>
       <c r="H5" s="30" t="s">
         <v>203</v>
@@ -31285,7 +31288,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F6" s="55">
         <v>20000</v>
@@ -31311,7 +31314,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F7" s="55">
         <v>20000</v>
@@ -31328,7 +31331,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C8" s="55">
         <v>62000</v>
@@ -31337,7 +31340,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F8" s="55">
         <v>20000</v>
@@ -31363,7 +31366,7 @@
         <v>15</v>
       </c>
       <c r="E9" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F9" s="55">
         <v>15000</v>
@@ -31389,7 +31392,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F10" s="55">
         <v>20000</v>
@@ -31415,7 +31418,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F11" s="55">
         <v>2000</v>
@@ -31441,7 +31444,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F12" s="55">
         <v>1000</v>
@@ -31467,7 +31470,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F13" s="55">
         <v>1000</v>
@@ -31493,7 +31496,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F14" s="55">
         <v>1000</v>
@@ -31519,7 +31522,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F15" s="55">
         <v>1000</v>
@@ -31545,7 +31548,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F16" s="55">
         <v>1000</v>
@@ -31562,7 +31565,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C17" s="55">
         <v>5000</v>
@@ -31571,7 +31574,7 @@
         <v>0.5</v>
       </c>
       <c r="E17" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F17" s="55">
         <v>500</v>
@@ -31597,7 +31600,7 @@
         <v>0.375</v>
       </c>
       <c r="E18" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F18" s="55">
         <v>375</v>
@@ -31623,7 +31626,7 @@
         <v>0.4</v>
       </c>
       <c r="E19" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F19" s="55">
         <v>400</v>
@@ -31640,7 +31643,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C20" s="55">
         <v>65000</v>
@@ -31649,7 +31652,7 @@
         <v>15</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F20" s="55">
         <v>15000</v>
@@ -31675,7 +31678,7 @@
         <v>3</v>
       </c>
       <c r="E21" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F21" s="55">
         <v>3000</v>
@@ -31701,7 +31704,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F22" s="55">
         <v>1000</v>
@@ -31727,7 +31730,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F23" s="55">
         <v>1000</v>
@@ -31753,7 +31756,7 @@
         <v>0.4</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F24" s="55">
         <v>400</v>
@@ -31779,7 +31782,7 @@
         <v>0.5</v>
       </c>
       <c r="E25" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F25" s="55">
         <v>500</v>
@@ -31796,7 +31799,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C26" s="55">
         <v>0</v>
@@ -31805,7 +31808,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F26" s="55">
         <v>3000</v>
@@ -31814,7 +31817,7 @@
         <f>IF(F26&gt;0,C26/F26,0)</f>
       </c>
       <c r="H26" s="86" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -31831,7 +31834,7 @@
         <v>2.5</v>
       </c>
       <c r="E27" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F27" s="55">
         <v>2500</v>
@@ -31857,7 +31860,7 @@
         <v>3.2</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F28" s="55">
         <v>3200</v>
@@ -31883,7 +31886,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F29" s="55">
         <v>2000</v>
@@ -31909,7 +31912,7 @@
         <v>5.9</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F30" s="55">
         <v>5900</v>
@@ -31935,7 +31938,7 @@
         <v>0.4</v>
       </c>
       <c r="E31" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F31" s="55">
         <v>400</v>
@@ -31961,7 +31964,7 @@
         <v>0.4</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F32" s="55">
         <v>400</v>
@@ -31987,7 +31990,7 @@
         <v>0.9</v>
       </c>
       <c r="E33" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F33" s="55">
         <v>900</v>
@@ -32013,7 +32016,7 @@
         <v>0.9</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F34" s="55">
         <v>900</v>
@@ -32039,7 +32042,7 @@
         <v>0.6</v>
       </c>
       <c r="E35" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F35" s="55">
         <v>600</v>
@@ -32065,7 +32068,7 @@
         <v>1.5</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F36" s="55">
         <v>1800</v>
@@ -32091,7 +32094,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F37" s="55">
         <v>15000</v>
@@ -32117,7 +32120,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F38" s="55">
         <v>15000</v>
@@ -32134,7 +32137,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C39" s="55">
         <v>196000</v>
@@ -32143,7 +32146,7 @@
         <v>25</v>
       </c>
       <c r="E39" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F39" s="55">
         <v>25000</v>
@@ -32169,7 +32172,7 @@
         <v>1.8</v>
       </c>
       <c r="E40" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F40" s="55">
         <v>1800</v>
@@ -32195,7 +32198,7 @@
         <v>13.1</v>
       </c>
       <c r="E41" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F41" s="55">
         <v>13100</v>
@@ -32212,7 +32215,7 @@
         <v>37</v>
       </c>
       <c r="B42" s="44" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C42" s="55">
         <v>6000</v>
@@ -32221,7 +32224,7 @@
         <v>13</v>
       </c>
       <c r="E42" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F42" s="55">
         <v>13000</v>
@@ -32247,7 +32250,7 @@
         <v>0.2</v>
       </c>
       <c r="E43" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F43" s="55">
         <v>200</v>
@@ -32264,7 +32267,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="44" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C44" s="55">
         <v>157500</v>
@@ -32273,7 +32276,7 @@
         <v>10.5</v>
       </c>
       <c r="E44" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F44" s="55">
         <v>10500</v>
@@ -32299,7 +32302,7 @@
         <v>0.9</v>
       </c>
       <c r="E45" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F45" s="55">
         <v>900</v>
@@ -32325,7 +32328,7 @@
         <v>0.9</v>
       </c>
       <c r="E46" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F46" s="55">
         <v>900</v>
@@ -32351,7 +32354,7 @@
         <v>0.2</v>
       </c>
       <c r="E47" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F47" s="55">
         <v>200</v>
@@ -32377,7 +32380,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F48" s="55">
         <v>1000</v>
@@ -32403,7 +32406,7 @@
         <v>0.2</v>
       </c>
       <c r="E49" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F49" s="55">
         <v>200</v>
@@ -32420,7 +32423,7 @@
         <v>45</v>
       </c>
       <c r="B50" s="44" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C50" s="55">
         <v>2500</v>
@@ -32429,7 +32432,7 @@
         <v>0.8</v>
       </c>
       <c r="E50" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F50" s="55">
         <v>800</v>
@@ -32446,7 +32449,7 @@
         <v>46</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C51" s="55">
         <v>2800</v>
@@ -32455,7 +32458,7 @@
         <v>0.8</v>
       </c>
       <c r="E51" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F51" s="55">
         <v>800</v>
@@ -32481,7 +32484,7 @@
         <v>1.6</v>
       </c>
       <c r="E52" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F52" s="55">
         <v>1600</v>
@@ -32507,7 +32510,7 @@
         <v>0.1</v>
       </c>
       <c r="E53" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F53" s="55">
         <v>100</v>
@@ -32533,7 +32536,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F54" s="55">
         <v>1000</v>
@@ -32559,7 +32562,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F55" s="55">
         <v>1000</v>
@@ -32585,7 +32588,7 @@
         <v>5</v>
       </c>
       <c r="E56" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F56" s="55">
         <v>5000</v>
@@ -32602,7 +32605,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C57" s="55">
         <v>2000</v>
@@ -32611,7 +32614,7 @@
         <v>0.05</v>
       </c>
       <c r="E57" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F57" s="55">
         <v>50</v>
@@ -32637,7 +32640,7 @@
         <v>1</v>
       </c>
       <c r="E58" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F58" s="55">
         <v>1000</v>
@@ -32663,7 +32666,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F59" s="55">
         <v>1000</v>
@@ -32689,7 +32692,7 @@
         <v>0.2</v>
       </c>
       <c r="E60" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F60" s="55">
         <v>200</v>
@@ -32715,7 +32718,7 @@
         <v>18</v>
       </c>
       <c r="E61" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F61" s="55">
         <v>18000</v>
@@ -32732,7 +32735,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="44" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C62" s="55">
         <v>24000</v>
@@ -32741,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F62" s="55">
         <v>1000</v>
@@ -32758,7 +32761,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="49" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C63" s="55">
         <v>21000</v>
@@ -32767,7 +32770,7 @@
         <v>0</v>
       </c>
       <c r="E63" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F63" s="55">
         <v>0</v>
@@ -32776,7 +32779,7 @@
         <f>IF(F63&gt;0,C63/F63,0)</f>
       </c>
       <c r="H63" s="87" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -32784,7 +32787,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="44" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C64" s="55">
         <v>19500</v>
@@ -32793,7 +32796,7 @@
         <v>0</v>
       </c>
       <c r="E64" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F64" s="55">
         <v>0</v>
@@ -32802,7 +32805,7 @@
         <f>IF(F64&gt;0,C64/F64,0)</f>
       </c>
       <c r="H64" s="86" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -32819,7 +32822,7 @@
         <v>0.1</v>
       </c>
       <c r="E65" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F65" s="55">
         <v>100</v>
@@ -32845,7 +32848,7 @@
         <v>0.9</v>
       </c>
       <c r="E66" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F66" s="55">
         <v>900</v>
@@ -32862,7 +32865,7 @@
         <v>62</v>
       </c>
       <c r="B67" s="49" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C67" s="55">
         <v>6000</v>
@@ -32871,7 +32874,7 @@
         <v>1.3</v>
       </c>
       <c r="E67" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F67" s="55">
         <v>1300</v>
@@ -32897,7 +32900,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F68" s="55">
         <v>1000</v>
@@ -32923,7 +32926,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F69" s="55">
         <v>1000</v>
@@ -32949,7 +32952,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F70" s="55">
         <v>1000</v>
@@ -32966,7 +32969,7 @@
         <v>66</v>
       </c>
       <c r="B71" s="49" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C71" s="55">
         <v>4400</v>
@@ -32975,7 +32978,7 @@
         <v>1</v>
       </c>
       <c r="E71" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F71" s="55">
         <v>1000</v>
@@ -33001,7 +33004,7 @@
         <v>18</v>
       </c>
       <c r="E72" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F72" s="55">
         <v>18000</v>
@@ -33018,7 +33021,7 @@
         <v>68</v>
       </c>
       <c r="B73" s="49" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C73" s="55">
         <v>11800</v>
@@ -33027,7 +33030,7 @@
         <v>5</v>
       </c>
       <c r="E73" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F73" s="55">
         <v>5000</v>
@@ -33044,7 +33047,7 @@
         <v>69</v>
       </c>
       <c r="B74" s="44" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C74" s="55">
         <v>75000</v>
@@ -33053,7 +33056,7 @@
         <v>10</v>
       </c>
       <c r="E74" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F74" s="55">
         <v>10000</v>
@@ -33079,7 +33082,7 @@
         <v>15</v>
       </c>
       <c r="E75" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F75" s="55">
         <v>15000</v>
@@ -33105,7 +33108,7 @@
         <v>22.8</v>
       </c>
       <c r="E76" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F76" s="55">
         <v>22800</v>
@@ -33122,7 +33125,7 @@
         <v>72</v>
       </c>
       <c r="B77" s="49" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C77" s="55">
         <v>5300</v>
@@ -33131,7 +33134,7 @@
         <v>0.55</v>
       </c>
       <c r="E77" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F77" s="55">
         <v>550</v>
@@ -33148,7 +33151,7 @@
         <v>73</v>
       </c>
       <c r="B78" s="44" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C78" s="55">
         <v>2125</v>
@@ -33157,7 +33160,7 @@
         <v>5</v>
       </c>
       <c r="E78" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F78" s="55">
         <v>5000</v>
@@ -33183,7 +33186,7 @@
         <v>0.2</v>
       </c>
       <c r="E79" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F79" s="55">
         <v>200</v>
@@ -33209,7 +33212,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F80" s="55">
         <v>0</v>
@@ -33218,7 +33221,7 @@
         <f>IF(F80&gt;0,C80/F80,0)</f>
       </c>
       <c r="H80" s="86" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -33226,7 +33229,7 @@
         <v>76</v>
       </c>
       <c r="B81" s="49" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C81" s="55">
         <v>2500</v>
@@ -33235,7 +33238,7 @@
         <v>0.1</v>
       </c>
       <c r="E81" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F81" s="55">
         <v>100</v>
@@ -33261,7 +33264,7 @@
         <v>0.2</v>
       </c>
       <c r="E82" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F82" s="55">
         <v>200</v>
@@ -33278,7 +33281,7 @@
         <v>78</v>
       </c>
       <c r="B83" s="49" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C83" s="55">
         <v>4500</v>
@@ -33287,7 +33290,7 @@
         <v>0.2</v>
       </c>
       <c r="E83" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F83" s="55">
         <v>200</v>
@@ -33304,7 +33307,7 @@
         <v>79</v>
       </c>
       <c r="B84" s="44" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C84" s="55">
         <v>21000</v>
@@ -33313,7 +33316,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F84" s="55">
         <v>0</v>
@@ -33322,7 +33325,7 @@
         <f>IF(F84&gt;0,C84/F84,0)</f>
       </c>
       <c r="H84" s="86" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -33339,7 +33342,7 @@
         <v>1</v>
       </c>
       <c r="E85" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F85" s="55">
         <v>1000</v>
@@ -33356,7 +33359,7 @@
         <v>81</v>
       </c>
       <c r="B86" s="44" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C86" s="55">
         <v>4200</v>
@@ -33365,7 +33368,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F86" s="55">
         <v>1000</v>
@@ -33391,7 +33394,7 @@
         <v>1</v>
       </c>
       <c r="E87" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F87" s="55">
         <v>1000</v>
@@ -33417,7 +33420,7 @@
         <v>3.3</v>
       </c>
       <c r="E88" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F88" s="55">
         <v>3300</v>
@@ -33434,7 +33437,7 @@
         <v>84</v>
       </c>
       <c r="B89" s="49" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C89" s="55">
         <v>7225</v>
@@ -33443,7 +33446,7 @@
         <v>2.8</v>
       </c>
       <c r="E89" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F89" s="55">
         <v>2800</v>
@@ -33469,7 +33472,7 @@
         <v>1</v>
       </c>
       <c r="E90" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F90" s="55">
         <v>1000</v>
@@ -33486,7 +33489,7 @@
         <v>86</v>
       </c>
       <c r="B91" s="49" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C91" s="55">
         <v>3200</v>
@@ -33495,7 +33498,7 @@
         <v>1</v>
       </c>
       <c r="E91" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F91" s="55">
         <v>1000</v>
@@ -33521,7 +33524,7 @@
         <v>0.065</v>
       </c>
       <c r="E92" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F92" s="55">
         <v>65</v>
@@ -33547,7 +33550,7 @@
         <v>1</v>
       </c>
       <c r="E93" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F93" s="55">
         <v>1000</v>
@@ -33573,7 +33576,7 @@
         <v>0.5</v>
       </c>
       <c r="E94" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F94" s="55">
         <v>500</v>
@@ -33590,7 +33593,7 @@
         <v>90</v>
       </c>
       <c r="B95" s="49" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C95" s="55">
         <v>24000</v>
@@ -33599,7 +33602,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F95" s="55">
         <v>20000</v>
@@ -33625,7 +33628,7 @@
         <v>0.2</v>
       </c>
       <c r="E96" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F96" s="55">
         <v>200</v>
@@ -33651,7 +33654,7 @@
         <v>5</v>
       </c>
       <c r="E97" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F97" s="55">
         <v>5000</v>
@@ -33677,7 +33680,7 @@
         <v>0.2</v>
       </c>
       <c r="E98" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F98" s="55">
         <v>200</v>
@@ -33703,7 +33706,7 @@
         <v>0.2</v>
       </c>
       <c r="E99" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F99" s="55">
         <v>200</v>
@@ -33720,7 +33723,7 @@
         <v>95</v>
       </c>
       <c r="B100" s="44" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C100" s="55">
         <v>60000</v>
@@ -33729,7 +33732,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F100" s="55">
         <v>0</v>
@@ -33738,7 +33741,7 @@
         <f>IF(F100&gt;0,C100/F100,0)</f>
       </c>
       <c r="H100" s="86" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -33746,7 +33749,7 @@
         <v>96</v>
       </c>
       <c r="B101" s="49" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C101" s="55">
         <v>64000</v>
@@ -33755,7 +33758,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F101" s="55">
         <v>0</v>
@@ -33764,7 +33767,7 @@
         <f>IF(F101&gt;0,C101/F101,0)</f>
       </c>
       <c r="H101" s="87" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -33772,7 +33775,7 @@
         <v>97</v>
       </c>
       <c r="B102" s="44" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C102" s="55">
         <v>63000</v>
@@ -33781,7 +33784,7 @@
         <v>0</v>
       </c>
       <c r="E102" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F102" s="55">
         <v>0</v>
@@ -33790,7 +33793,7 @@
         <f>IF(F102&gt;0,C102/F102,0)</f>
       </c>
       <c r="H102" s="86" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -33807,7 +33810,7 @@
         <v>0.835</v>
       </c>
       <c r="E103" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F103" s="55">
         <v>835</v>
@@ -33833,7 +33836,7 @@
         <v>0.565</v>
       </c>
       <c r="E104" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F104" s="55">
         <v>565</v>
@@ -33850,7 +33853,7 @@
         <v>100</v>
       </c>
       <c r="B105" s="49" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C105" s="55">
         <v>11900</v>
@@ -33859,7 +33862,7 @@
         <v>0.21</v>
       </c>
       <c r="E105" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F105" s="55">
         <v>210</v>
@@ -33885,7 +33888,7 @@
         <v>1</v>
       </c>
       <c r="E106" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F106" s="55">
         <v>1000</v>
@@ -33911,7 +33914,7 @@
         <v>0.08</v>
       </c>
       <c r="E107" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F107" s="55">
         <v>80</v>
@@ -33937,7 +33940,7 @@
         <v>0.45</v>
       </c>
       <c r="E108" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F108" s="55">
         <v>450</v>
@@ -33963,7 +33966,7 @@
         <v>0.8</v>
       </c>
       <c r="E109" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F109" s="55">
         <v>800</v>
@@ -33989,7 +33992,7 @@
         <v>0.8</v>
       </c>
       <c r="E110" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F110" s="55">
         <v>800</v>
@@ -34015,7 +34018,7 @@
         <v>2</v>
       </c>
       <c r="E111" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F111" s="55">
         <v>2000</v>
@@ -34041,7 +34044,7 @@
         <v>0.5</v>
       </c>
       <c r="E112" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F112" s="55">
         <v>500</v>
@@ -34067,7 +34070,7 @@
         <v>0.55</v>
       </c>
       <c r="E113" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F113" s="55">
         <v>550</v>
@@ -34093,7 +34096,7 @@
         <v>3</v>
       </c>
       <c r="E114" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F114" s="55">
         <v>3000</v>
@@ -34119,7 +34122,7 @@
         <v>0.5</v>
       </c>
       <c r="E115" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F115" s="55">
         <v>500</v>
@@ -34145,7 +34148,7 @@
         <v>0.1</v>
       </c>
       <c r="E116" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F116" s="55">
         <v>100</v>
@@ -34162,7 +34165,7 @@
         <v>112</v>
       </c>
       <c r="B117" s="49" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C117" s="55">
         <v>3200</v>
@@ -34171,7 +34174,7 @@
         <v>1</v>
       </c>
       <c r="E117" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F117" s="55">
         <v>1000</v>
@@ -34188,7 +34191,7 @@
         <v>113</v>
       </c>
       <c r="B118" s="44" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C118" s="55">
         <v>23500</v>
@@ -34197,7 +34200,7 @@
         <v>1</v>
       </c>
       <c r="E118" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F118" s="55">
         <v>1000</v>
@@ -34223,7 +34226,7 @@
         <v>1</v>
       </c>
       <c r="E119" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F119" s="55">
         <v>1000</v>
@@ -34249,7 +34252,7 @@
         <v>0.15</v>
       </c>
       <c r="E120" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F120" s="55">
         <v>150</v>
@@ -34275,7 +34278,7 @@
         <v>2.4</v>
       </c>
       <c r="E121" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F121" s="55">
         <v>2400</v>
@@ -34301,7 +34304,7 @@
         <v>3.2</v>
       </c>
       <c r="E122" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F122" s="55">
         <v>3200</v>
@@ -34336,7 +34339,7 @@
         <f>IF(F123&gt;0,C123/F123,0)</f>
       </c>
       <c r="H123" s="87" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -34371,7 +34374,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -34383,7 +34386,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -34395,7 +34398,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -34410,22 +34413,22 @@
         <v>96</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>200</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H5" s="30" t="s">
         <v>203</v>
@@ -34592,7 +34595,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C12" s="55">
         <v>900</v>
@@ -34670,7 +34673,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C15" s="55">
         <v>549</v>
@@ -34696,7 +34699,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C16" s="55">
         <v>2000</v>
@@ -34719,7 +34722,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -34731,16 +34734,16 @@
     </row>
     <row r="20" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B20" s="30" t="s">
         <v>195</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E20" s="30" t="s">
         <v>201</v>
@@ -34823,7 +34826,7 @@
         <v>204</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D24" s="55">
         <v>3000</v>
@@ -34883,7 +34886,7 @@
         <v>204</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D27" s="55">
         <v>200</v>
@@ -35023,7 +35026,7 @@
         <v>204</v>
       </c>
       <c r="C34" s="49" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D34" s="55">
         <v>1000</v>
@@ -35323,7 +35326,7 @@
         <v>204</v>
       </c>
       <c r="C49" s="49" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D49" s="55">
         <v>1000</v>
@@ -35497,7 +35500,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="44" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B58" s="53" t="s">
         <v>204</v>
@@ -35517,7 +35520,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="44" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B59" s="53" t="s">
         <v>204</v>
@@ -35897,7 +35900,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="49" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B78" s="63" t="s">
         <v>204</v>
@@ -35917,7 +35920,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="49" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B79" s="63" t="s">
         <v>204</v>
@@ -35937,7 +35940,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="49" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B80" s="63" t="s">
         <v>204</v>
@@ -35957,7 +35960,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="49" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B81" s="63" t="s">
         <v>204</v>
@@ -35977,7 +35980,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="49" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B82" s="63" t="s">
         <v>204</v>
@@ -35997,7 +36000,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="49" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B83" s="63" t="s">
         <v>204</v>
@@ -36017,7 +36020,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="49" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B84" s="63" t="s">
         <v>209</v>
@@ -36037,7 +36040,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="49" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B85" s="63" t="s">
         <v>204</v>
@@ -36057,13 +36060,13 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="44" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B86" s="53" t="s">
         <v>204</v>
       </c>
       <c r="C86" s="44" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D86" s="55">
         <v>200</v>
@@ -36077,7 +36080,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="44" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B87" s="53" t="s">
         <v>209</v>
@@ -36097,7 +36100,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="44" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B88" s="53" t="s">
         <v>204</v>
@@ -36117,7 +36120,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="44" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B89" s="53" t="s">
         <v>396</v>
@@ -36174,7 +36177,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -36183,7 +36186,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -36195,16 +36198,16 @@
         <v>96</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -36212,16 +36215,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C6" s="55">
         <v>12000000</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -36229,16 +36232,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C7" s="55">
         <v>205800</v>
       </c>
       <c r="D7" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E7" s="64" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -36246,16 +36249,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C8" s="55">
         <v>2336970</v>
       </c>
       <c r="D8" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -36263,16 +36266,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C9" s="55">
         <v>783420</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E9" s="64" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -36280,16 +36283,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C10" s="55">
         <v>8800000</v>
       </c>
       <c r="D10" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -36297,16 +36300,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C11" s="55">
         <v>50000</v>
       </c>
       <c r="D11" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E11" s="64" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -36314,16 +36317,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C12" s="55">
         <v>3894139</v>
       </c>
       <c r="D12" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E12" s="54" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -36331,16 +36334,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C13" s="55">
         <v>17000000</v>
       </c>
       <c r="D13" s="88" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E13" s="87" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -36348,16 +36351,16 @@
         <v>9</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C14" s="55">
         <v>204000</v>
       </c>
       <c r="D14" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E14" s="54" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -36365,16 +36368,16 @@
         <v>10</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C15" s="55">
         <v>391270</v>
       </c>
       <c r="D15" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="64" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -36382,16 +36385,16 @@
         <v>11</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C16" s="55">
         <v>703730</v>
       </c>
       <c r="D16" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E16" s="54" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -36399,16 +36402,16 @@
         <v>12</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C17" s="55">
         <v>48950</v>
       </c>
       <c r="D17" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E17" s="64" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -36416,21 +36419,21 @@
         <v>13</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C18" s="55">
         <v>256800</v>
       </c>
       <c r="D18" s="88" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E18" s="86" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="89" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B19" s="89"/>
       <c r="C19" s="90">
@@ -36438,12 +36441,12 @@
       </c>
       <c r="D19" s="91"/>
       <c r="E19" s="92" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="89" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B20" s="89"/>
       <c r="C20" s="90">
@@ -36451,12 +36454,12 @@
       </c>
       <c r="D20" s="91"/>
       <c r="E20" s="92" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -36465,20 +36468,20 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="93" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B23" s="93"/>
       <c r="C23" s="88" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D23" s="44"/>
       <c r="E23" s="54" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="93" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B24" s="93"/>
       <c r="C24" s="73">
@@ -36486,12 +36489,12 @@
       </c>
       <c r="D24" s="44"/>
       <c r="E24" s="54" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="93" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B25" s="93"/>
       <c r="C25" s="94">
@@ -36499,12 +36502,12 @@
       </c>
       <c r="D25" s="44"/>
       <c r="E25" s="54" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="93" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B26" s="93"/>
       <c r="C26" s="55">
@@ -36512,12 +36515,12 @@
       </c>
       <c r="D26" s="44"/>
       <c r="E26" s="54" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="93" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B27" s="93"/>
       <c r="C27" s="57">
@@ -36525,7 +36528,7 @@
       </c>
       <c r="D27" s="44"/>
       <c r="E27" s="54" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -36538,12 +36541,12 @@
       </c>
       <c r="D28" s="44"/>
       <c r="E28" s="54" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="93" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B29" s="93"/>
       <c r="C29" s="73">
@@ -36551,12 +36554,12 @@
       </c>
       <c r="D29" s="44"/>
       <c r="E29" s="54" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="93" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B30" s="93"/>
       <c r="C30" s="73">
@@ -36564,7 +36567,7 @@
       </c>
       <c r="D30" s="44"/>
       <c r="E30" s="54" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -36616,7 +36619,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -36625,7 +36628,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -36640,13 +36643,13 @@
         <v>195</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -36654,7 +36657,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="95" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>106</v>
@@ -36663,7 +36666,7 @@
         <v>238</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -36671,7 +36674,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="96" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C6" s="49" t="s">
         <v>127</v>
@@ -36680,7 +36683,7 @@
         <v>238</v>
       </c>
       <c r="E6" s="64" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -36688,7 +36691,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="95" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C7" s="44" t="s">
         <v>149</v>
@@ -36697,7 +36700,7 @@
         <v>238</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -36705,7 +36708,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="96" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C8" s="49" t="s">
         <v>153</v>
@@ -36714,7 +36717,7 @@
         <v>238</v>
       </c>
       <c r="E8" s="64" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -36722,7 +36725,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="95" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C9" s="44" t="s">
         <v>154</v>
@@ -36731,7 +36734,7 @@
         <v>238</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -36739,16 +36742,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="96" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C10" s="49" t="s">
         <v>167</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E10" s="64" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -36756,7 +36759,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="95" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C11" s="44" t="s">
         <v>167</v>
@@ -36765,7 +36768,7 @@
         <v>397</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -36773,16 +36776,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="96" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C12" s="49" t="s">
         <v>170</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E12" s="64" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -36790,16 +36793,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="95" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C13" s="44" t="s">
         <v>171</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E13" s="54" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -36807,16 +36810,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="96" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C14" s="49" t="s">
         <v>172</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E14" s="64" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -36824,16 +36827,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="95" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C15" s="44" t="s">
         <v>173</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E15" s="54" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -36841,16 +36844,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="96" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C16" s="49" t="s">
         <v>174</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E16" s="64" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -36858,16 +36861,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="95" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C17" s="44" t="s">
         <v>176</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E17" s="54" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -36875,16 +36878,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="96" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C18" s="49" t="s">
         <v>181</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E18" s="64" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -36892,16 +36895,16 @@
         <v>15</v>
       </c>
       <c r="B19" s="95" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E19" s="54" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -36909,16 +36912,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="96" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E20" s="64" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -36926,16 +36929,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="95" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E21" s="54" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -36943,16 +36946,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="96" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D22" s="49" t="s">
         <v>405</v>
       </c>
       <c r="E22" s="64" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -36960,16 +36963,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="95" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E23" s="54" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -36977,16 +36980,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="96" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E24" s="64" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -36994,16 +36997,16 @@
         <v>21</v>
       </c>
       <c r="B25" s="95" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E25" s="54" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -37011,16 +37014,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="96" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E26" s="64" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -37028,16 +37031,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="95" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D27" s="44" t="s">
         <v>420</v>
       </c>
       <c r="E27" s="54" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -37045,16 +37048,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="96" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E28" s="64" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -37062,16 +37065,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="95" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E29" s="54" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
